--- a/data/PIPELINE2_RESULTADOS.xlsx
+++ b/data/PIPELINE2_RESULTADOS.xlsx
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>64.09999999999999</v>
+        <v>68.25</v>
       </c>
       <c r="E161" t="n">
-        <v>57.7</v>
+        <v>62.6</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 64% | conf 58%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 68% | conf 63%)</t>
         </is>
       </c>
     </row>
@@ -44664,10 +44664,10 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>55.01</v>
+        <v>56.04</v>
       </c>
       <c r="D161" t="n">
-        <v>28.4</v>
+        <v>30.1</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -44676,14 +44676,14 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 55% | conf 28% | odd 1.48)</t>
+          <t>🟡 Ambas Marcam (prob 56% | conf 30% | odd 1.48)</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>62.3</v>
+        <v>59.26</v>
       </c>
       <c r="H161" t="n">
-        <v>41.4</v>
+        <v>36.7</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -44692,14 +44692,14 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 62% | conf 41% | odd 16.75)</t>
+          <t>🟡 Lay 0x0 (prob 59% | conf 37% | odd 16.75)</t>
         </is>
       </c>
       <c r="K161" t="n">
-        <v>49.02</v>
+        <v>49.13</v>
       </c>
       <c r="L161" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -44712,10 +44712,10 @@
         </is>
       </c>
       <c r="O161" t="n">
-        <v>72.83</v>
+        <v>73.77</v>
       </c>
       <c r="P161" t="n">
-        <v>57.5</v>
+        <v>59</v>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
@@ -44724,14 +44724,14 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>🔥 Lay 1x0 (prob 73% | conf 58% | odd 13.25)</t>
+          <t>🔥 Lay 1x0 (prob 74% | conf 59% | odd 13.25)</t>
         </is>
       </c>
       <c r="S161" t="n">
-        <v>96.55</v>
+        <v>95.53</v>
       </c>
       <c r="T161" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -44740,14 +44740,14 @@
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 10.00)</t>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 10.00)</t>
         </is>
       </c>
       <c r="W161" t="n">
-        <v>31.39</v>
+        <v>34.07</v>
       </c>
       <c r="X161" t="n">
-        <v>13.1</v>
+        <v>16.6</v>
       </c>
       <c r="Y161" t="inlineStr">
         <is>
@@ -44756,14 +44756,14 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Fora (4+) (prob 31% | conf 13%)</t>
+          <t>⚠️ Lay Goleada Fora (4+) (prob 34% | conf 17%)</t>
         </is>
       </c>
       <c r="AA161" t="n">
-        <v>64.09999999999999</v>
+        <v>68.25</v>
       </c>
       <c r="AB161" t="n">
-        <v>57.7</v>
+        <v>62.6</v>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
@@ -44772,14 +44772,14 @@
       </c>
       <c r="AD161" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 64% | conf 58%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 68% | conf 63%)</t>
         </is>
       </c>
       <c r="AE161" t="n">
-        <v>55.16</v>
+        <v>54.47</v>
       </c>
       <c r="AF161" t="n">
-        <v>26.7</v>
+        <v>25.6</v>
       </c>
       <c r="AG161" t="inlineStr">
         <is>
@@ -44788,14 +44788,14 @@
       </c>
       <c r="AH161" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 55% | conf 27% | odd 1.25)</t>
+          <t>🟡 Over 0.5 HT (prob 54% | conf 26% | odd 1.25)</t>
         </is>
       </c>
       <c r="AI161" t="n">
-        <v>60.62</v>
+        <v>61.15</v>
       </c>
       <c r="AJ161" t="n">
-        <v>39.8</v>
+        <v>40.6</v>
       </c>
       <c r="AK161" t="inlineStr">
         <is>
@@ -44804,14 +44804,14 @@
       </c>
       <c r="AL161" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 61% | conf 40% | odd 1.12)</t>
+          <t>🟡 Over 1.5 FT (prob 61% | conf 41% | odd 1.12)</t>
         </is>
       </c>
       <c r="AM161" t="n">
-        <v>57.27</v>
+        <v>56.47</v>
       </c>
       <c r="AN161" t="n">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -44820,14 +44820,14 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 57% | conf 31% | odd 1.52)</t>
+          <t>🟡 Over 2.5 FT (prob 56% | conf 29% | odd 1.52)</t>
         </is>
       </c>
       <c r="AQ161" t="n">
-        <v>44.71</v>
+        <v>44.47</v>
       </c>
       <c r="AR161" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
@@ -44836,14 +44836,14 @@
       </c>
       <c r="AT161" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 45% | conf 19%)</t>
+          <t>⚠️ Under 1.5 HT (prob 44% | conf 19%)</t>
         </is>
       </c>
       <c r="AU161" t="n">
-        <v>43.26</v>
+        <v>43.79</v>
       </c>
       <c r="AV161" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 43% | conf 12% | odd 2.46)</t>
+          <t>⚠️ Under 2.5 FT (prob 44% | conf 13% | odd 2.46)</t>
         </is>
       </c>
     </row>

--- a/data/PIPELINE2_RESULTADOS.xlsx
+++ b/data/PIPELINE2_RESULTADOS.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,12 +469,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Santa Clara U23</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Portimonense U23</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70.86</v>
+        <v>63.62</v>
       </c>
       <c r="E2" t="n">
-        <v>63.1</v>
+        <v>54</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -495,31 +495,31 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 71% | conf 63%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 54%)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wigan Athletic U21</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coventry City U21</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAY10</t>
+          <t>LAYGA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>75.78</v>
+        <v>65.42</v>
       </c>
       <c r="E3" t="n">
-        <v>62.1</v>
+        <v>56.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -528,64 +528,64 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🔥 Lay 1x0 (prob 76% | conf 62% | odd 21.00)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 65% | conf 56%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Charlton Athletic U21</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sheffield United U21</t>
+          <t>São Tomé and Príncipe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAY10</t>
+          <t>LAYGA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>67.75</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>49.5</v>
+        <v>79.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 68% | conf 50% | odd 13.33)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 84% | conf 80%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skjetten</t>
+          <t>OH Leuven W</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Skjervoy</t>
+          <t>Roma W</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAY00</t>
+          <t>LAYGH</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74.67</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>60.6</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -594,31 +594,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🔥 Lay 0x0 (prob 75% | conf 61% | odd 41.00)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 77% | conf 72%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Academico Viseu U23</t>
+          <t>Servette Chênois W</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Estoril U23</t>
+          <t>OL Lyonnes W</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAYGA</t>
+          <t>LAY10</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61.37</v>
+        <v>77.94</v>
       </c>
       <c r="E6" t="n">
-        <v>51.1</v>
+        <v>65.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -627,64 +627,64 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 61% | conf 51%)</t>
+          <t>🔥 Lay 1x0 (prob 78% | conf 66% | odd 9.00)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bayern Munich W</t>
+          <t>Madureira</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manchester City W</t>
+          <t>Sampaio Corrêa RJ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LAY10</t>
+          <t>LAYGH</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>71.8</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>55.9</v>
+        <v>82.3</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>🔥 Lay 1x0 (prob 72% | conf 56% | odd 7.33)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 85% | conf 82%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Inter Milano W</t>
+          <t>Grêmio Prudente U20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Juventus-BR U20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAYGA</t>
+          <t>LAYGH</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63.88</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>54.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -693,52 +693,52 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 54%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 78% | conf 74%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bristol City U21</t>
+          <t>Saguntino</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hull City U21</t>
+          <t>Navalcarnero</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAY00</t>
+          <t>LAYGH</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73.45999999999999</v>
+        <v>85.91</v>
       </c>
       <c r="E9" t="n">
-        <v>58.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>🔥 Lay 0x0 (prob 73% | conf 59% | odd 27.33)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 86% | conf 83%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arsenal W</t>
+          <t>West Ham United U21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Koge</t>
+          <t>Valencia U21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79.23999999999999</v>
+        <v>64.34</v>
       </c>
       <c r="E10" t="n">
-        <v>73.7</v>
+        <v>54.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -759,19 +759,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 79% | conf 74%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 55%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Juventus W</t>
+          <t>Middlesbrough U21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SL Benfica W</t>
+          <t>Genk U21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>65.59</v>
+        <v>68</v>
       </c>
       <c r="E11" t="n">
-        <v>56.4</v>
+        <v>59.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -792,52 +792,52 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 66% | conf 56%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 68% | conf 60%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Turks and Caicos Islands</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paris SG W</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAYGA</t>
+          <t>LAYGH</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>68.69</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>60.4</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 69% | conf 60%)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 84% | conf 81%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Chelsea W</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Internacional Palmira</t>
+          <t>Austria Wien W</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -846,43 +846,43 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>65.72</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>56.6</v>
+        <v>81</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 66% | conf 57%)</t>
+          <t>🔥🔥 Lay Goleada Fora (4+) (prob 85% | conf 81%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Atlético</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Paris W</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LAYGH</t>
+          <t>LAYGA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>85.15000000000001</v>
+        <v>86.56</v>
       </c>
       <c r="E14" t="n">
-        <v>82.5</v>
+        <v>83</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -891,19 +891,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>🔥🔥 Lay Goleada Casa (4+) (prob 85% | conf 82%)</t>
+          <t>🔥🔥 Lay Goleada Fora (4+) (prob 87% | conf 83%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Real San Andres</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Cienciano</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>74.29000000000001</v>
+        <v>73.88</v>
       </c>
       <c r="E15" t="n">
-        <v>69.7</v>
+        <v>69.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -924,52 +924,52 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 74% | conf 70%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 74% | conf 69%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Saint Martin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAYGA</t>
+          <t>LAYGH</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>76.98999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="E16" t="n">
-        <v>70.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 77% | conf 71%)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 87% | conf 84%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba</t>
+          <t>Nação</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -978,31 +978,31 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>80.39</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>75.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 80% | conf 75%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 77% | conf 71%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55.58</v>
+        <v>59.76</v>
       </c>
       <c r="E18" t="n">
-        <v>47.6</v>
+        <v>52.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1023,31 +1023,31 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 56% | conf 48%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 60% | conf 53%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LAYGH</t>
+          <t>LAYGA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>77.88</v>
+        <v>61.53</v>
       </c>
       <c r="E19" t="n">
-        <v>73.90000000000001</v>
+        <v>51.3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1056,7 +1056,172 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 78% | conf 74%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 62% | conf 51%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LAYGA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 82% | conf 77%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Firpo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cacahuatique</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LAYGA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="E21" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 69% | conf 61%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Alianza</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fuerte San Francisco</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LAYGA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 78% | conf 72%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>LAYGA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 55%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>LAYGA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="E24" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 62% | conf 52%)</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX19"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,19 +1494,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Santa Clara U23</t>
+          <t>Birmingham Legion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Portimonense U23</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53.98</v>
+        <v>59.11</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8</v>
+        <v>34.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1350,14 +1515,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 54% | conf 27% | odd 1.67)</t>
+          <t>🟡 Ambas Marcam (prob 59% | conf 35% | odd 1.47)</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>56.83</v>
+        <v>64.55</v>
       </c>
       <c r="H2" t="n">
-        <v>32.9</v>
+        <v>44.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1366,14 +1531,14 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 57% | conf 33% | odd 11.00)</t>
+          <t>🟡 Lay 0x0 (prob 65% | conf 45% | odd 15.83)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>53.02</v>
+        <v>53.95</v>
       </c>
       <c r="L2" t="n">
-        <v>12.9</v>
+        <v>14.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -1382,14 +1547,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 53% | conf 13% | odd 11.67)</t>
+          <t>⚠️ Lay 0x1 (prob 54% | conf 15% | odd 14.33)</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>48.03</v>
+        <v>60.64</v>
       </c>
       <c r="P2" t="n">
-        <v>18.7</v>
+        <v>38.4</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1398,30 +1563,30 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>⚠️ Lay 1x0 (prob 48% | conf 19% | odd 7.00)</t>
+          <t>🟡 Lay 1x0 (prob 61% | conf 38% | odd 9.00)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>95.53</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 12.33)</t>
+          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 10.00)</t>
         </is>
       </c>
       <c r="W2" t="n">
-        <v>70.86</v>
+        <v>63.62</v>
       </c>
       <c r="X2" t="n">
-        <v>63.1</v>
+        <v>54</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1430,14 +1595,14 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 71% | conf 63%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 54%)</t>
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>52.4</v>
+        <v>37.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.9</v>
+        <v>26.7</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -1446,14 +1611,14 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 52% | conf 44%)</t>
+          <t>🟡 Lay Goleada Casa (4+) (prob 38% | conf 27%)</t>
         </is>
       </c>
       <c r="AE2" t="n">
-        <v>51.34</v>
+        <v>57.96</v>
       </c>
       <c r="AF2" t="n">
-        <v>20.4</v>
+        <v>31.3</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -1462,14 +1627,14 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 51% | conf 20% | odd 1.31)</t>
+          <t>🟡 Over 0.5 HT (prob 58% | conf 31% | odd 1.21)</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>52.03</v>
+        <v>63.08</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.7</v>
+        <v>43.6</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -1478,14 +1643,14 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 52% | conf 27% | odd 1.20)</t>
+          <t>🟡 Over 1.5 FT (prob 63% | conf 44% | odd 1.12)</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>50.96</v>
+        <v>60.34</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.4</v>
+        <v>35.6</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1494,14 +1659,14 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>⚠️ Over 2.5 FT (prob 51% | conf 20% | odd 1.74)</t>
+          <t>🟡 Over 2.5 FT (prob 60% | conf 36% | odd 1.46)</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>49.96</v>
+        <v>44.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1510,14 +1675,14 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>🟡 Under 1.5 HT (prob 50% | conf 27%)</t>
+          <t>⚠️ Under 1.5 HT (prob 44% | conf 18%)</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>48.65</v>
+        <v>38.71</v>
       </c>
       <c r="AV2" t="n">
-        <v>20.8</v>
+        <v>5.5</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
@@ -1526,26 +1691,26 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 49% | conf 21% | odd 2.00)</t>
+          <t>⚠️ Under 2.5 FT (prob 39% | conf 6% | odd 2.55)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wigan Athletic U21</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coventry City U21</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>64.43000000000001</v>
+        <v>51.51</v>
       </c>
       <c r="D3" t="n">
-        <v>43.4</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1554,14 +1719,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 64% | conf 43% | odd 1.21)</t>
+          <t>⚠️ Ambas Marcam (prob 52% | conf 23% | odd 1.86)</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>72.05</v>
+        <v>56.53</v>
       </c>
       <c r="H3" t="n">
-        <v>56.6</v>
+        <v>32.4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1570,14 +1735,14 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>🔥 Lay 0x0 (prob 72% | conf 57% | odd 36.67)</t>
+          <t>🟡 Lay 0x0 (prob 57% | conf 32% | odd 9.43)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>56.94</v>
+        <v>50.93</v>
       </c>
       <c r="L3" t="n">
-        <v>20.2</v>
+        <v>9</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1586,14 +1751,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 57% | conf 20% | odd 21.67)</t>
+          <t>⚠️ Lay 0x1 (prob 51% | conf 9% | odd 11.33)</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>75.78</v>
+        <v>56.55</v>
       </c>
       <c r="P3" t="n">
-        <v>62.1</v>
+        <v>32</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1602,30 +1767,30 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>🔥 Lay 1x0 (prob 76% | conf 62% | odd 21.00)</t>
+          <t>🟡 Lay 1x0 (prob 57% | conf 32% | odd 6.00)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>93.45999999999999</v>
+        <v>95.53</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 9.33)</t>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 13.67)</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>37.23</v>
+        <v>65.42</v>
       </c>
       <c r="X3" t="n">
-        <v>20.5</v>
+        <v>56.2</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1634,14 +1799,14 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Fora (4+) (prob 37% | conf 20%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 65% | conf 56%)</t>
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>29.5</v>
+        <v>51.48</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.9</v>
+        <v>42.8</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -1650,14 +1815,14 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Casa (4+) (prob 30% | conf 17%)</t>
+          <t>🟡 Lay Goleada Casa (4+) (prob 51% | conf 43%)</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>67.20999999999999</v>
+        <v>49.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>46.4</v>
+        <v>16.8</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -1666,14 +1831,14 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 67% | conf 46% | odd 1.08)</t>
+          <t>⚠️ Over 0.5 HT (prob 49% | conf 17% | odd 1.37)</t>
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>73.97</v>
+        <v>52.27</v>
       </c>
       <c r="AJ3" t="n">
-        <v>60.2</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
@@ -1682,14 +1847,14 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>🔥 Over 1.5 FT (prob 74% | conf 60% | odd 1.02)</t>
+          <t>🟡 Over 1.5 FT (prob 52% | conf 27% | odd 1.28)</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>73.34999999999999</v>
+        <v>47.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>56.8</v>
+        <v>15.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1698,14 +1863,14 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>🔥 Over 2.5 FT (prob 73% | conf 57% | odd 1.16)</t>
+          <t>⚠️ Over 2.5 FT (prob 48% | conf 15% | odd 2.02)</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>34.05</v>
+        <v>50.91</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.4</v>
+        <v>28.1</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1714,14 +1879,14 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 34% | conf 3%)</t>
+          <t>🟡 Under 1.5 HT (prob 51% | conf 28%)</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>23.8</v>
+        <v>51.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>17.5</v>
+        <v>25.2</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1730,26 +1895,26 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>❌ Sem sinal — Under 2.5 FT (prob 24% | odd 4.38)</t>
+          <t>🟡 Under 2.5 FT (prob 52% | conf 25% | odd 1.84)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Charlton Athletic U21</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sheffield United U21</t>
+          <t>São Tomé and Príncipe</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61.72</v>
+        <v>44.3</v>
       </c>
       <c r="D4" t="n">
-        <v>39.1</v>
+        <v>11.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1758,14 +1923,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 62% | conf 39% | odd 1.38)</t>
+          <t>⚠️ Ambas Marcam (prob 44% | conf 11% | odd 1.97)</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>60.13</v>
+        <v>63.43</v>
       </c>
       <c r="H4" t="n">
-        <v>38</v>
+        <v>43.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1774,14 +1939,14 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 60% | conf 38% | odd 19.50)</t>
+          <t>🟡 Lay 0x0 (prob 63% | conf 43% | odd 12.00)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>51.01</v>
+        <v>58.98</v>
       </c>
       <c r="L4" t="n">
-        <v>9.199999999999999</v>
+        <v>23.9</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1790,14 +1955,14 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 51% | conf 9% | odd 13.00)</t>
+          <t>⚠️ Lay 0x1 (prob 59% | conf 24% | odd 17.67)</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>67.75</v>
+        <v>41.15</v>
       </c>
       <c r="P4" t="n">
-        <v>49.5</v>
+        <v>7.9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1806,46 +1971,46 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 68% | conf 50% | odd 13.33)</t>
+          <t>⚠️ Lay 1x0 (prob 41% | conf 8% | odd 6.50)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>93.45999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 9.17)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 17.33)</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>36.51</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>19.6</v>
+        <v>79.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Fora (4+) (prob 37% | conf 20%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 84% | conf 80%)</t>
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>48.48</v>
+        <v>25.64</v>
       </c>
       <c r="AB4" t="n">
-        <v>39.3</v>
+        <v>12.3</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1854,14 +2019,14 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 48% | conf 39%)</t>
+          <t>⚠️ Lay Goleada Casa (4+) (prob 26% | conf 12%)</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>56.87</v>
+        <v>54.99</v>
       </c>
       <c r="AF4" t="n">
-        <v>29.5</v>
+        <v>26.4</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
@@ -1870,14 +2035,14 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 57% | conf 30% | odd 1.21)</t>
+          <t>🟡 Over 0.5 HT (prob 55% | conf 26% | odd 1.28)</t>
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>60.96</v>
+        <v>56.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40.3</v>
+        <v>33.2</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1886,14 +2051,14 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 61% | conf 40% | odd 1.08)</t>
+          <t>🟡 Over 1.5 FT (prob 56% | conf 33% | odd 1.18)</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>61.63</v>
+        <v>55.66</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.7</v>
+        <v>28.1</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1902,14 +2067,14 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 62% | conf 38% | odd 1.40)</t>
+          <t>🟡 Over 2.5 FT (prob 56% | conf 28% | odd 1.73)</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>42.04</v>
+        <v>45.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>15.1</v>
+        <v>20.5</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1918,14 +2083,14 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 42% | conf 15%)</t>
+          <t>⚠️ Under 1.5 HT (prob 46% | conf 20%)</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>38.72</v>
+        <v>43.02</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.5</v>
+        <v>12.2</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -1934,26 +2099,26 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 39% | conf 6% | odd 2.76)</t>
+          <t>⚠️ Under 2.5 FT (prob 43% | conf 12% | odd 2.18)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Skjetten</t>
+          <t>OH Leuven W</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Skjervoy</t>
+          <t>Roma W</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62.56</v>
+        <v>53.7</v>
       </c>
       <c r="D5" t="n">
-        <v>40.4</v>
+        <v>26.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1962,14 +2127,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 63% | conf 40% | odd 1.30)</t>
+          <t>🟡 Ambas Marcam (prob 54% | conf 26% | odd 1.66)</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>74.67</v>
+        <v>59.11</v>
       </c>
       <c r="H5" t="n">
-        <v>60.6</v>
+        <v>36.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1978,14 +2143,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>🔥 Lay 0x0 (prob 75% | conf 61% | odd 41.00)</t>
+          <t>🟡 Lay 0x0 (prob 59% | conf 36% | odd 13.17)</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>59.68</v>
+        <v>49.36</v>
       </c>
       <c r="L5" t="n">
-        <v>25.2</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1994,14 +2159,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x1 (prob 60% | conf 25% | odd 32.00)</t>
+          <t>⚠️ Lay 0x1 (prob 49% | conf 6% | odd 7.50)</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>70.66</v>
+        <v>69.78</v>
       </c>
       <c r="P5" t="n">
-        <v>54.1</v>
+        <v>52.7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -2010,14 +2175,14 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>🔥 Lay 1x0 (prob 71% | conf 54% | odd 15.67)</t>
+          <t>🔥 Lay 1x0 (prob 70% | conf 53% | odd 12.33)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>96.55</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>4.6</v>
+        <v>1.2</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -2026,14 +2191,14 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 97% | conf 5% | odd 10.33)</t>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 12.33)</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>58.4</v>
+        <v>39.68</v>
       </c>
       <c r="X5" t="n">
-        <v>47.3</v>
+        <v>23.6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -2042,14 +2207,14 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Fora (4+) (prob 58% | conf 47%)</t>
+          <t>⚠️ Lay Goleada Fora (4+) (prob 40% | conf 24%)</t>
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>19.16</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2058,14 +2223,14 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Casa (4+) (prob 19% | conf 5%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 77% | conf 72%)</t>
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>70.81999999999999</v>
+        <v>54.49</v>
       </c>
       <c r="AF5" t="n">
-        <v>52.3</v>
+        <v>25.6</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -2074,14 +2239,14 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>🔥 Over 0.5 HT (prob 71% | conf 52% | odd 1.11)</t>
+          <t>🟡 Over 0.5 HT (prob 54% | conf 26% | odd 1.26)</t>
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>73.09999999999999</v>
+        <v>56.68</v>
       </c>
       <c r="AJ5" t="n">
-        <v>58.9</v>
+        <v>33.8</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -2090,14 +2255,14 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>🔥 Over 1.5 FT (prob 73% | conf 59% | odd 1.02)</t>
+          <t>🟡 Over 1.5 FT (prob 57% | conf 34% | odd 1.18)</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.66</v>
+        <v>55.52</v>
       </c>
       <c r="AN5" t="n">
-        <v>60.5</v>
+        <v>27.8</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2106,14 +2271,14 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>🔥 Over 2.5 FT (prob 76% | conf 60% | odd 1.19)</t>
+          <t>🟡 Over 2.5 FT (prob 56% | conf 28% | odd 1.62)</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>29.89</v>
+        <v>45.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.6</v>
+        <v>19.7</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2122,14 +2287,14 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>❌ Sem sinal — Under 1.5 HT (prob 30%)</t>
+          <t>⚠️ Under 1.5 HT (prob 45% | conf 20%)</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>23.81</v>
+        <v>43.98</v>
       </c>
       <c r="AV5" t="n">
-        <v>17.5</v>
+        <v>13.6</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
@@ -2138,26 +2303,26 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>❌ Sem sinal — Under 2.5 FT (prob 24% | odd 4.08)</t>
+          <t>⚠️ Under 2.5 FT (prob 44% | conf 14% | odd 2.20)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Academico Viseu U23</t>
+          <t>Servette Chênois W</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Estoril U23</t>
+          <t>OL Lyonnes W</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.78</v>
+        <v>41.9</v>
       </c>
       <c r="D6" t="n">
-        <v>29.6</v>
+        <v>7.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2166,14 +2331,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 56% | conf 30% | odd 1.59)</t>
+          <t>⚠️ Ambas Marcam (prob 42% | conf 8% | odd 4.00)</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>54.82</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>29.8</v>
+        <v>57.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2182,14 +2347,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 55% | conf 30% | odd 11.33)</t>
+          <t>🔥 Lay 0x0 (prob 73% | conf 58% | odd 12.00)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>52.19</v>
+        <v>54.87</v>
       </c>
       <c r="L6" t="n">
-        <v>11.3</v>
+        <v>16.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2198,14 +2363,14 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 52% | conf 11% | odd 10.67)</t>
+          <t>⚠️ Lay 0x1 (prob 55% | conf 16% | odd 11.33)</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>54.25</v>
+        <v>77.94</v>
       </c>
       <c r="P6" t="n">
-        <v>28.4</v>
+        <v>65.5</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -2214,14 +2379,14 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 54% | conf 28% | odd 7.67)</t>
+          <t>🔥 Lay 1x0 (prob 78% | conf 66% | odd 9.00)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>95.53</v>
+        <v>96.55</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -2230,14 +2395,14 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 11.00)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 13.67)</t>
         </is>
       </c>
       <c r="W6" t="n">
-        <v>61.37</v>
+        <v>58</v>
       </c>
       <c r="X6" t="n">
-        <v>51.1</v>
+        <v>46.8</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2246,14 +2411,14 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 61% | conf 51%)</t>
+          <t>🟡 Lay Goleada Fora (4+) (prob 58% | conf 47%)</t>
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>51.5</v>
+        <v>63.89</v>
       </c>
       <c r="AB6" t="n">
-        <v>42.8</v>
+        <v>57.4</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -2262,14 +2427,14 @@
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 52% | conf 43%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 64% | conf 57%)</t>
         </is>
       </c>
       <c r="AE6" t="n">
-        <v>51.76</v>
+        <v>65.53</v>
       </c>
       <c r="AF6" t="n">
-        <v>21.1</v>
+        <v>43.6</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
@@ -2278,14 +2443,14 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 52% | conf 21% | odd 1.30)</t>
+          <t>🟡 Over 0.5 HT (prob 66% | conf 44% | odd 1.28)</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>54.57</v>
+        <v>68.34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>30.6</v>
+        <v>51.6</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -2294,14 +2459,14 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 55% | conf 31% | odd 1.19)</t>
+          <t>🔥 Over 1.5 FT (prob 68% | conf 52% | odd 1.19)</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>51.97</v>
+        <v>72.94</v>
       </c>
       <c r="AN6" t="n">
-        <v>22.1</v>
+        <v>56.1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2310,14 +2475,14 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>⚠️ Over 2.5 FT (prob 52% | conf 22% | odd 1.66)</t>
+          <t>🔥 Over 2.5 FT (prob 73% | conf 56% | odd 1.11)</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>49.38</v>
+        <v>36.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>25.9</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2326,14 +2491,14 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>🟡 Under 1.5 HT (prob 49% | conf 26%)</t>
+          <t>⚠️ Under 1.5 HT (prob 36% | conf 7%)</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>48.52</v>
+        <v>30.27</v>
       </c>
       <c r="AV6" t="n">
-        <v>20.6</v>
+        <v>7.5</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -2342,26 +2507,26 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 49% | conf 21% | odd 2.12)</t>
+          <t>❌ Sem sinal — Under 2.5 FT (prob 30% | odd 6.00)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bayern Munich W</t>
+          <t>Madureira</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Manchester City W</t>
+          <t>Sampaio Corrêa RJ</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>56.72</v>
+        <v>43.75</v>
       </c>
       <c r="D7" t="n">
-        <v>31.1</v>
+        <v>10.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2370,14 +2535,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 57% | conf 31% | odd 1.40)</t>
+          <t>⚠️ Ambas Marcam (prob 44% | conf 10% | odd 2.10)</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>66.93000000000001</v>
+        <v>38.77</v>
       </c>
       <c r="H7" t="n">
-        <v>48.6</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -2386,14 +2551,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 67% | conf 49% | odd 12.08)</t>
+          <t>⚠️ Lay 0x0 (prob 39% | conf 5% | odd 5.80)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>55.07</v>
+        <v>45.85</v>
       </c>
       <c r="L7" t="n">
-        <v>16.7</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2402,14 +2567,14 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 55% | conf 17% | odd 11.17)</t>
+          <t>❌ Sem sinal — Lay 0x1 (prob 46% | odd 6.17)</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>71.8</v>
+        <v>43.68</v>
       </c>
       <c r="P7" t="n">
-        <v>55.9</v>
+        <v>11.9</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -2418,14 +2583,14 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>🔥 Lay 1x0 (prob 72% | conf 56% | odd 7.33)</t>
+          <t>⚠️ Lay 1x0 (prob 44% | conf 12% | odd 5.67)</t>
         </is>
       </c>
       <c r="S7" t="n">
         <v>95.53</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -2434,14 +2599,14 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 11.66)</t>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 15.00)</t>
         </is>
       </c>
       <c r="W7" t="n">
-        <v>56.5</v>
+        <v>69.08</v>
       </c>
       <c r="X7" t="n">
-        <v>44.9</v>
+        <v>60.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2450,30 +2615,30 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Fora (4+) (prob 56% | conf 45%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 69% | conf 61%)</t>
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>40.77</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="AB7" t="n">
-        <v>30.2</v>
+        <v>82.3</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 41% | conf 30%)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 85% | conf 82%)</t>
         </is>
       </c>
       <c r="AE7" t="n">
-        <v>58.16</v>
+        <v>42.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>31.6</v>
+        <v>5.7</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
@@ -2482,14 +2647,14 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 58% | conf 32% | odd 1.29)</t>
+          <t>⚠️ Over 0.5 HT (prob 42% | conf 6% | odd 1.54)</t>
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>65.33</v>
+        <v>38.29</v>
       </c>
       <c r="AJ7" t="n">
-        <v>47</v>
+        <v>5.7</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
@@ -2498,14 +2663,14 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 65% | conf 47% | odd 1.19)</t>
+          <t>⚠️ Over 1.5 FT (prob 38% | conf 6% | odd 1.50)</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>62.2</v>
+        <v>35.58</v>
       </c>
       <c r="AN7" t="n">
-        <v>38.7</v>
+        <v>4.5</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -2514,14 +2679,14 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 62% | conf 39% | odd 1.40)</t>
+          <t>❌ Sem sinal — Over 2.5 FT (prob 36% | odd 2.57)</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>41.51</v>
+        <v>62.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.4</v>
+        <v>44.8</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -2530,14 +2695,14 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 42% | conf 14%)</t>
+          <t>🟡 Under 1.5 HT (prob 62% | conf 45%)</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>37.49</v>
+        <v>65.44</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.6</v>
+        <v>46.7</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
@@ -2546,26 +2711,26 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 37% | conf 4% | odd 2.75)</t>
+          <t>🟡 Under 2.5 FT (prob 65% | conf 47% | odd 1.44)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Inter Milano W</t>
+          <t>Grêmio Prudente U20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Juventus-BR U20</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.72</v>
+        <v>55.48</v>
       </c>
       <c r="D8" t="n">
-        <v>32.7</v>
+        <v>29.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2574,14 +2739,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 58% | conf 33% | odd 1.66)</t>
+          <t>🟡 Ambas Marcam (prob 55% | conf 29% | odd 1.61)</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>59.52</v>
+        <v>54.74</v>
       </c>
       <c r="H8" t="n">
-        <v>37.1</v>
+        <v>29.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2590,14 +2755,14 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 60% | conf 37% | odd 12.08)</t>
+          <t>🟡 Lay 0x0 (prob 55% | conf 30% | odd 11.50)</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>51.79</v>
+        <v>48.35</v>
       </c>
       <c r="L8" t="n">
-        <v>10.6</v>
+        <v>4.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2606,14 +2771,14 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 52% | conf 11% | odd 11.17)</t>
+          <t>⚠️ Lay 0x1 (prob 48% | conf 4% | odd 8.00)</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>56.5</v>
+        <v>67.73</v>
       </c>
       <c r="P8" t="n">
-        <v>31.9</v>
+        <v>49.5</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -2622,14 +2787,14 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 56% | conf 32% | odd 7.33)</t>
+          <t>🟡 Lay 1x0 (prob 68% | conf 50% | odd 10.00)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>96.55</v>
+        <v>95.53</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -2638,14 +2803,14 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 11.66)</t>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 11.00)</t>
         </is>
       </c>
       <c r="W8" t="n">
-        <v>63.88</v>
+        <v>36.99</v>
       </c>
       <c r="X8" t="n">
-        <v>54.3</v>
+        <v>20.2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2654,14 +2819,14 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 54%)</t>
+          <t>⚠️ Lay Goleada Fora (4+) (prob 37% | conf 20%)</t>
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>58.43</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>51</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -2670,14 +2835,14 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 58% | conf 51%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 78% | conf 74%)</t>
         </is>
       </c>
       <c r="AE8" t="n">
-        <v>51.83</v>
+        <v>52.81</v>
       </c>
       <c r="AF8" t="n">
-        <v>21.2</v>
+        <v>22.9</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
@@ -2686,14 +2851,14 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 52% | conf 21% | odd 1.29)</t>
+          <t>⚠️ Over 0.5 HT (prob 53% | conf 23% | odd 1.28)</t>
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>56.94</v>
+        <v>54.02</v>
       </c>
       <c r="AJ8" t="n">
-        <v>34.2</v>
+        <v>29.7</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
@@ -2702,14 +2867,14 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 57% | conf 34% | odd 1.19)</t>
+          <t>🟡 Over 1.5 FT (prob 54% | conf 30% | odd 1.19)</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>53.27</v>
+        <v>53.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -2718,14 +2883,14 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>⚠️ Over 2.5 FT (prob 53% | conf 24% | odd 1.80)</t>
+          <t>⚠️ Over 2.5 FT (prob 54% | conf 25% | odd 1.72)</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>48.04</v>
+        <v>50.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>23.9</v>
+        <v>27.4</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -2734,14 +2899,14 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 48% | conf 24%)</t>
+          <t>🟡 Under 1.5 HT (prob 50% | conf 27%)</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>46.28</v>
+        <v>48.27</v>
       </c>
       <c r="AV8" t="n">
-        <v>17.2</v>
+        <v>20.3</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
@@ -2750,26 +2915,26 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 46% | conf 17% | odd 2.00)</t>
+          <t>⚠️ Under 2.5 FT (prob 48% | conf 20% | odd 2.02)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bristol City U21</t>
+          <t>Saguntino</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hull City U21</t>
+          <t>Navalcarnero</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>61.37</v>
+        <v>45.02</v>
       </c>
       <c r="D9" t="n">
-        <v>38.5</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2778,14 +2943,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 61% | conf 38% | odd 1.31)</t>
+          <t>⚠️ Ambas Marcam (prob 45% | conf 12% | odd 1.85)</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>73.45999999999999</v>
+        <v>42.38</v>
       </c>
       <c r="H9" t="n">
-        <v>58.8</v>
+        <v>10.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2794,14 +2959,14 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>🔥 Lay 0x0 (prob 73% | conf 59% | odd 27.33)</t>
+          <t>⚠️ Lay 0x0 (prob 42% | conf 10% | odd 7.17)</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>56.28</v>
+        <v>46.24</v>
       </c>
       <c r="L9" t="n">
-        <v>18.9</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2810,14 +2975,14 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 56% | conf 19% | odd 24.00)</t>
+          <t>⚠️ Lay 0x1 (prob 46% | conf 0% | odd 6.17)</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>67.91</v>
+        <v>47.98</v>
       </c>
       <c r="P9" t="n">
-        <v>49.8</v>
+        <v>18.6</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -2826,30 +2991,30 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 68% | conf 50% | odd 15.00)</t>
+          <t>⚠️ Lay 1x0 (prob 48% | conf 19% | odd 7.33)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>93.45999999999999</v>
+        <v>95.53</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 11.00)</t>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 12.33)</t>
         </is>
       </c>
       <c r="W9" t="n">
-        <v>57.48</v>
+        <v>53.98</v>
       </c>
       <c r="X9" t="n">
-        <v>46.2</v>
+        <v>41.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2858,30 +3023,30 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Fora (4+) (prob 57% | conf 46%)</t>
+          <t>🟡 Lay Goleada Fora (4+) (prob 54% | conf 42%)</t>
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>27.7</v>
+        <v>85.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Casa (4+) (prob 28% | conf 15%)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 86% | conf 83%)</t>
         </is>
       </c>
       <c r="AE9" t="n">
-        <v>65.55</v>
+        <v>44.53</v>
       </c>
       <c r="AF9" t="n">
-        <v>43.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -2890,14 +3055,14 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 66% | conf 44% | odd 1.11)</t>
+          <t>⚠️ Over 0.5 HT (prob 45% | conf 9% | odd 1.43)</t>
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>70.93000000000001</v>
+        <v>40.17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>55.6</v>
+        <v>8.5</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -2906,14 +3071,14 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>🔥 Over 1.5 FT (prob 71% | conf 56% | odd 1.02)</t>
+          <t>⚠️ Over 1.5 FT (prob 40% | conf 8% | odd 1.38)</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>69.14</v>
+        <v>39.87</v>
       </c>
       <c r="AN9" t="n">
-        <v>49.9</v>
+        <v>2.4</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -2922,14 +3087,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 69% | conf 50% | odd 1.23)</t>
+          <t>⚠️ Over 2.5 FT (prob 40% | conf 2% | odd 2.20)</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>34.42</v>
+        <v>57.26</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>37.4</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -2938,14 +3103,14 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 34% | conf 4%)</t>
+          <t>🟡 Under 1.5 HT (prob 57% | conf 37%)</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>29.67</v>
+        <v>61.06</v>
       </c>
       <c r="AV9" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
@@ -2954,26 +3119,26 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>❌ Sem sinal — Under 2.5 FT (prob 30% | odd 3.69)</t>
+          <t>🟡 Under 2.5 FT (prob 61% | conf 40% | odd 1.60)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Arsenal W</t>
+          <t>West Ham United U21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Koge</t>
+          <t>Valencia U21</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>40.35</v>
+        <v>49.34</v>
       </c>
       <c r="D10" t="n">
-        <v>5.1</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2982,14 +3147,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 40% | conf 5% | odd 2.62)</t>
+          <t>⚠️ Ambas Marcam (prob 49% | conf 19% | odd 1.87)</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>73.98</v>
+        <v>55.03</v>
       </c>
       <c r="H10" t="n">
-        <v>59.6</v>
+        <v>30.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -2998,14 +3163,14 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>🔥 Lay 0x0 (prob 74% | conf 60% | odd 12.08)</t>
+          <t>🟡 Lay 0x0 (prob 55% | conf 30% | odd 12.00)</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>61.93</v>
+        <v>52.14</v>
       </c>
       <c r="L10" t="n">
-        <v>29.4</v>
+        <v>11.2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3014,14 +3179,14 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x1 (prob 62% | conf 29% | odd 11.17)</t>
+          <t>⚠️ Lay 0x1 (prob 52% | conf 11% | odd 11.33)</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>58.75</v>
+        <v>55.83</v>
       </c>
       <c r="P10" t="n">
-        <v>35.5</v>
+        <v>30.9</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -3030,14 +3195,14 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 59% | conf 36% | odd 7.33)</t>
+          <t>🟡 Lay 1x0 (prob 56% | conf 31% | odd 9.00)</t>
         </is>
       </c>
       <c r="S10" t="n">
         <v>96.55</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -3046,14 +3211,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 97% | conf 3% | odd 11.66)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 13.67)</t>
         </is>
       </c>
       <c r="W10" t="n">
-        <v>79.23999999999999</v>
+        <v>64.34</v>
       </c>
       <c r="X10" t="n">
-        <v>73.7</v>
+        <v>54.9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -3062,14 +3227,14 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 79% | conf 74%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 55%)</t>
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>22.68</v>
+        <v>55.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.9</v>
+        <v>47.5</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -3078,14 +3243,14 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Casa (4+) (prob 23% | conf 9%)</t>
+          <t>🟡 Lay Goleada Casa (4+) (prob 55% | conf 48%)</t>
         </is>
       </c>
       <c r="AE10" t="n">
-        <v>66.27</v>
+        <v>52.63</v>
       </c>
       <c r="AF10" t="n">
-        <v>44.9</v>
+        <v>22.6</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -3094,14 +3259,14 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 66% | conf 45% | odd 1.29)</t>
+          <t>⚠️ Over 0.5 HT (prob 53% | conf 23% | odd 1.28)</t>
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>76.54000000000001</v>
+        <v>53.74</v>
       </c>
       <c r="AJ10" t="n">
-        <v>64.09999999999999</v>
+        <v>29.3</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -3110,14 +3275,14 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>🔥 Over 1.5 FT (prob 77% | conf 64% | odd 1.19)</t>
+          <t>🟡 Over 1.5 FT (prob 54% | conf 29% | odd 1.19)</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>68.2</v>
+        <v>52.88</v>
       </c>
       <c r="AN10" t="n">
-        <v>48.4</v>
+        <v>23.5</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -3126,14 +3291,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 68% | conf 48% | odd 1.30)</t>
+          <t>⚠️ Over 2.5 FT (prob 53% | conf 24% | odd 1.69)</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>35.21</v>
+        <v>48.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>24.8</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -3142,14 +3307,14 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 35% | conf 5%)</t>
+          <t>⚠️ Under 1.5 HT (prob 49% | conf 25%)</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>31.74</v>
+        <v>45.59</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>16.1</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
@@ -3158,26 +3323,26 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>❌ Sem sinal — Under 2.5 FT (prob 32% | odd 3.40)</t>
+          <t>⚠️ Under 2.5 FT (prob 46% | conf 16% | odd 2.13)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Juventus W</t>
+          <t>Middlesbrough U21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SL Benfica W</t>
+          <t>Genk U21</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>52.38</v>
+        <v>50.72</v>
       </c>
       <c r="D11" t="n">
-        <v>24.2</v>
+        <v>21.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3186,14 +3351,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 52% | conf 24% | odd 1.72)</t>
+          <t>⚠️ Ambas Marcam (prob 51% | conf 22% | odd 1.87)</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>60.55</v>
+        <v>56.72</v>
       </c>
       <c r="H11" t="n">
-        <v>38.7</v>
+        <v>32.7</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -3202,14 +3367,14 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 61% | conf 39% | odd 12.08)</t>
+          <t>🟡 Lay 0x0 (prob 57% | conf 33% | odd 12.00)</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>55.34</v>
+        <v>53.22</v>
       </c>
       <c r="L11" t="n">
-        <v>17.2</v>
+        <v>13.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3218,14 +3383,14 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 55% | conf 17% | odd 11.17)</t>
+          <t>⚠️ Lay 0x1 (prob 53% | conf 13% | odd 11.33)</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>62.26</v>
+        <v>53.57</v>
       </c>
       <c r="P11" t="n">
-        <v>41</v>
+        <v>27.4</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -3234,30 +3399,30 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 62% | conf 41% | odd 7.33)</t>
+          <t>🟡 Lay 1x0 (prob 54% | conf 27% | odd 9.00)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>95.53</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>⭐⭐⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 11.66)</t>
+          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 13.67)</t>
         </is>
       </c>
       <c r="W11" t="n">
-        <v>65.59</v>
+        <v>68</v>
       </c>
       <c r="X11" t="n">
-        <v>56.4</v>
+        <v>59.5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -3266,14 +3431,14 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 66% | conf 56%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 68% | conf 60%)</t>
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>42.95</v>
+        <v>50.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>32.8</v>
+        <v>42.1</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -3282,14 +3447,14 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 43% | conf 33%)</t>
+          <t>🟡 Lay Goleada Casa (4+) (prob 51% | conf 42%)</t>
         </is>
       </c>
       <c r="AE11" t="n">
-        <v>56.38</v>
+        <v>53.76</v>
       </c>
       <c r="AF11" t="n">
-        <v>28.7</v>
+        <v>24.4</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -3298,14 +3463,14 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 56% | conf 29% | odd 1.29)</t>
+          <t>⚠️ Over 0.5 HT (prob 54% | conf 24% | odd 1.28)</t>
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>58.99</v>
+        <v>55.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>37.3</v>
+        <v>31.4</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -3314,14 +3479,14 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 59% | conf 37% | odd 1.19)</t>
+          <t>🟡 Over 1.5 FT (prob 55% | conf 31% | odd 1.19)</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>54.28</v>
+        <v>55.03</v>
       </c>
       <c r="AN11" t="n">
-        <v>25.8</v>
+        <v>27</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -3330,14 +3495,14 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 54% | conf 26% | odd 1.70)</t>
+          <t>🟡 Over 2.5 FT (prob 55% | conf 27% | odd 1.69)</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>47.77</v>
+        <v>47.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -3346,14 +3511,14 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 48% | conf 24%)</t>
+          <t>⚠️ Under 1.5 HT (prob 47% | conf 23%)</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>45.16</v>
+        <v>44.74</v>
       </c>
       <c r="AV11" t="n">
-        <v>15.5</v>
+        <v>14.8</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
@@ -3362,26 +3527,26 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 45% | conf 16% | odd 2.10)</t>
+          <t>⚠️ Under 2.5 FT (prob 45% | conf 15% | odd 2.13)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Turks and Caicos Islands</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paris SG W</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>51.89</v>
+        <v>38.54</v>
       </c>
       <c r="D12" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -3390,14 +3555,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 52% | conf 23% | odd 1.66)</t>
+          <t>⚠️ Ambas Marcam (prob 39% | conf 2% | odd 2.14)</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>57.97</v>
+        <v>69.22</v>
       </c>
       <c r="H12" t="n">
-        <v>34.7</v>
+        <v>52.2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -3406,14 +3571,14 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 58% | conf 35% | odd 12.08)</t>
+          <t>🔥 Lay 0x0 (prob 69% | conf 52% | odd 20.33)</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>56.43</v>
+        <v>47.89</v>
       </c>
       <c r="L12" t="n">
-        <v>19.2</v>
+        <v>3.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3422,14 +3587,14 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 56% | conf 19% | odd 11.17)</t>
+          <t>⚠️ Lay 0x1 (prob 48% | conf 3% | odd 8.00)</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>52.11</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>25.1</v>
+        <v>65</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -3438,14 +3603,14 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 52% | conf 25% | odd 7.33)</t>
+          <t>🔥 Lay 1x0 (prob 78% | conf 65% | odd 37.67)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>95.53</v>
+        <v>96.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3454,14 +3619,14 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 11.66)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 24.00)</t>
         </is>
       </c>
       <c r="W12" t="n">
-        <v>68.69</v>
+        <v>36.36</v>
       </c>
       <c r="X12" t="n">
-        <v>60.4</v>
+        <v>19.4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -3470,30 +3635,30 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 69% | conf 60%)</t>
+          <t>⚠️ Lay Goleada Fora (4+) (prob 36% | conf 19%)</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>37.66</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>26.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 38% | conf 26%)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 84% | conf 81%)</t>
         </is>
       </c>
       <c r="AE12" t="n">
-        <v>55.9</v>
+        <v>57.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>27.9</v>
+        <v>30.7</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -3502,14 +3667,14 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 56% | conf 28% | odd 1.29)</t>
+          <t>🟡 Over 0.5 HT (prob 58% | conf 31% | odd 1.17)</t>
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>57.26</v>
+        <v>63.36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>34.7</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
@@ -3518,14 +3683,14 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 57% | conf 35% | odd 1.19)</t>
+          <t>🟡 Over 1.5 FT (prob 63% | conf 44% | odd 1.08)</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>54.92</v>
+        <v>65.56</v>
       </c>
       <c r="AN12" t="n">
-        <v>26.8</v>
+        <v>44.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -3534,14 +3699,14 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 55% | conf 27% | odd 1.61)</t>
+          <t>🟡 Over 2.5 FT (prob 66% | conf 44% | odd 1.38)</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>45.07</v>
+        <v>39.56</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -3550,14 +3715,14 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 45% | conf 20%)</t>
+          <t>⚠️ Under 1.5 HT (prob 40% | conf 12%)</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>44.18</v>
+        <v>33.89</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
@@ -3566,26 +3731,26 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 44% | conf 14% | odd 2.25)</t>
+          <t>❌ Sem sinal — Under 2.5 FT (prob 34% | odd 2.78)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Chelsea W</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Internacional Palmira</t>
+          <t>Austria Wien W</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>50.39</v>
+        <v>33.51</v>
       </c>
       <c r="D13" t="n">
-        <v>21.1</v>
+        <v>5.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -3594,30 +3759,30 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 50% | conf 21% | odd 1.66)</t>
+          <t>❌ Sem sinal — Ambas Marcam (prob 34% | odd 3.67)</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>43.61</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>12.4</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x0 (prob 44% | conf 12% | odd 12.08)</t>
+          <t>🔥 Lay 0x0 (prob 83% | conf 73% | odd 31.33)</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>50.3</v>
+        <v>65.14</v>
       </c>
       <c r="L13" t="n">
-        <v>7.9</v>
+        <v>35.4</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3626,14 +3791,14 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 50% | conf 8% | odd 11.17)</t>
+          <t>🟡 Lay 0x1 (prob 65% | conf 35% | odd 99.00)</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>50.26</v>
+        <v>65.7</v>
       </c>
       <c r="P13" t="n">
-        <v>22.2</v>
+        <v>46.3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -3642,14 +3807,14 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>⚠️ Lay 1x0 (prob 50% | conf 22% | odd 7.33)</t>
+          <t>🟡 Lay 1x0 (prob 66% | conf 46% | odd 11.67)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>95.53</v>
+        <v>96.55</v>
       </c>
       <c r="T13" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -3658,30 +3823,30 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 11.66)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 4% | odd 67.33)</t>
         </is>
       </c>
       <c r="W13" t="n">
-        <v>65.72</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>56.6</v>
+        <v>81</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 66% | conf 57%)</t>
+          <t>🔥🔥 Lay Goleada Fora (4+) (prob 85% | conf 81%)</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>60.36</v>
+        <v>14.51</v>
       </c>
       <c r="AB13" t="n">
-        <v>53.3</v>
+        <v>0.8</v>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
@@ -3690,14 +3855,14 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 60% | conf 53%)</t>
+          <t>❌ Sem sinal — Lay Goleada Casa (4+) (prob 15%)</t>
         </is>
       </c>
       <c r="AE13" t="n">
-        <v>45.72</v>
+        <v>69.53</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.3</v>
+        <v>50.2</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -3706,14 +3871,14 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 46% | conf 11% | odd 1.29)</t>
+          <t>🔥 Over 0.5 HT (prob 70% | conf 50% | odd 1.10)</t>
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>46.06</v>
+        <v>76.55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>17.6</v>
+        <v>64.2</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
@@ -3722,14 +3887,14 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>⚠️ Over 1.5 FT (prob 46% | conf 18% | odd 1.19)</t>
+          <t>🔥 Over 1.5 FT (prob 77% | conf 64% | odd 1.02)</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>40.58</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.6</v>
+        <v>57.5</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -3738,14 +3903,14 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>⚠️ Over 2.5 FT (prob 41% | conf 4% | odd 2.37)</t>
+          <t>🔥 Over 2.5 FT (prob 74% | conf 58% | odd 1.16)</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>55.73</v>
+        <v>31.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>35.2</v>
+        <v>0.1</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -3754,14 +3919,14 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>🟡 Under 1.5 HT (prob 56% | conf 35%)</t>
+          <t>⚠️ Under 1.5 HT (prob 32% | conf 0%)</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>59.8</v>
+        <v>23.29</v>
       </c>
       <c r="AV13" t="n">
-        <v>38</v>
+        <v>18.2</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
@@ -3770,26 +3935,26 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>🟡 Under 2.5 FT (prob 60% | conf 38% | odd 1.53)</t>
+          <t>❌ Sem sinal — Under 2.5 FT (prob 23% | odd 4.42)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Atlético</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Paris W</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>46.6</v>
+        <v>33.69</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -3798,30 +3963,30 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 47% | conf 15% | odd 1.98)</t>
+          <t>❌ Sem sinal — Ambas Marcam (prob 34% | odd 3.17)</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>46.98</v>
+        <v>84.55</v>
       </c>
       <c r="H14" t="n">
-        <v>17.6</v>
+        <v>76</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x0 (prob 47% | conf 18% | odd 6.40)</t>
+          <t>🔥 Lay 0x0 (prob 85% | conf 76% | odd 38.83)</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>46.12</v>
+        <v>62.31</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1</v>
+        <v>30.1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3830,14 +3995,14 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 46% | conf 0% | odd 5.83)</t>
+          <t>🟡 Lay 0x1 (prob 62% | conf 30% | odd 125.67)</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>51.01</v>
+        <v>74.56</v>
       </c>
       <c r="P14" t="n">
-        <v>23.4</v>
+        <v>60.2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -3846,14 +4011,14 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>⚠️ Lay 1x0 (prob 51% | conf 23% | odd 6.17)</t>
+          <t>🔥 Lay 1x0 (prob 75% | conf 60% | odd 19.67)</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>95.53</v>
+        <v>96.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3862,46 +4027,46 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 13.67)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 4% | odd 87.33)</t>
         </is>
       </c>
       <c r="W14" t="n">
-        <v>72.42</v>
+        <v>86.56</v>
       </c>
       <c r="X14" t="n">
-        <v>65.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 72% | conf 65%)</t>
+          <t>🔥🔥 Lay Goleada Fora (4+) (prob 87% | conf 83%)</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>85.15000000000001</v>
+        <v>11.34</v>
       </c>
       <c r="AB14" t="n">
-        <v>82.5</v>
+        <v>4.5</v>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>🔥🔥 Lay Goleada Casa (4+) (prob 85% | conf 82%)</t>
+          <t>❌ Sem sinal — Lay Goleada Casa (4+) (prob 11%)</t>
         </is>
       </c>
       <c r="AE14" t="n">
-        <v>45.02</v>
+        <v>68.83</v>
       </c>
       <c r="AF14" t="n">
-        <v>10.1</v>
+        <v>49</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -3910,14 +4075,14 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 45% | conf 10% | odd 1.50)</t>
+          <t>🟡 Over 0.5 HT (prob 69% | conf 49% | odd 1.08)</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>40.49</v>
+        <v>77.56</v>
       </c>
       <c r="AJ14" t="n">
-        <v>9</v>
+        <v>65.7</v>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
@@ -3926,14 +4091,14 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>⚠️ Over 1.5 FT (prob 40% | conf 9% | odd 1.45)</t>
+          <t>🔥 Over 1.5 FT (prob 78% | conf 66% | odd 1.01)</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>41.44</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="AN14" t="n">
-        <v>5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -3942,14 +4107,14 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>⚠️ Over 2.5 FT (prob 41% | conf 5% | odd 2.42)</t>
+          <t>🔥 Over 2.5 FT (prob 78% | conf 64% | odd 1.10)</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>57.33</v>
+        <v>31.45</v>
       </c>
       <c r="AR14" t="n">
-        <v>37.5</v>
+        <v>0.4</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -3958,14 +4123,14 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>🟡 Under 1.5 HT (prob 57% | conf 38%)</t>
+          <t>❌ Sem sinal — Under 1.5 HT (prob 31%)</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>59.8</v>
+        <v>19.62</v>
       </c>
       <c r="AV14" t="n">
-        <v>38</v>
+        <v>23.9</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
@@ -3974,26 +4139,26 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>🟡 Under 2.5 FT (prob 60% | conf 38% | odd 1.50)</t>
+          <t>❌ Sem sinal — Under 2.5 FT (prob 20% | odd 6.00)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Real San Andres</t>
+          <t>ADT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Orsomarso</t>
+          <t>Cienciano</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>46.44</v>
+        <v>55.47</v>
       </c>
       <c r="D15" t="n">
-        <v>14.8</v>
+        <v>29.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4002,14 +4167,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 46% | conf 15% | odd 1.84)</t>
+          <t>🟡 Ambas Marcam (prob 55% | conf 29% | odd 1.60)</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>43.52</v>
+        <v>55.6</v>
       </c>
       <c r="H15" t="n">
-        <v>12.2</v>
+        <v>31</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -4018,14 +4183,14 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x0 (prob 44% | conf 12% | odd 7.20)</t>
+          <t>🟡 Lay 0x0 (prob 56% | conf 31% | odd 11.00)</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>50.01</v>
+        <v>47.39</v>
       </c>
       <c r="L15" t="n">
-        <v>7.3</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4034,14 +4199,14 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 50% | conf 7% | odd 7.00)</t>
+          <t>⚠️ Lay 0x1 (prob 47% | conf 2% | odd 8.00)</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>43.43</v>
+        <v>59.9</v>
       </c>
       <c r="P15" t="n">
-        <v>11.5</v>
+        <v>37.3</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -4050,14 +4215,14 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>⚠️ Lay 1x0 (prob 43% | conf 12% | odd 6.17)</t>
+          <t>🟡 Lay 1x0 (prob 60% | conf 37% | odd 9.00)</t>
         </is>
       </c>
       <c r="S15" t="n">
         <v>93.45999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -4066,14 +4231,14 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 12.33)</t>
+          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 10.33)</t>
         </is>
       </c>
       <c r="W15" t="n">
-        <v>70.64</v>
+        <v>53.79</v>
       </c>
       <c r="X15" t="n">
-        <v>62.8</v>
+        <v>41.5</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -4082,14 +4247,14 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 71% | conf 63%)</t>
+          <t>🟡 Lay Goleada Fora (4+) (prob 54% | conf 42%)</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>74.29000000000001</v>
+        <v>73.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>69.7</v>
+        <v>69.2</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -4098,14 +4263,14 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 74% | conf 70%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 74% | conf 69%)</t>
         </is>
       </c>
       <c r="AE15" t="n">
-        <v>45.85</v>
+        <v>50.91</v>
       </c>
       <c r="AF15" t="n">
-        <v>11.5</v>
+        <v>19.7</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
@@ -4114,14 +4279,14 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 46% | conf 12% | odd 1.41)</t>
+          <t>⚠️ Over 0.5 HT (prob 51% | conf 20% | odd 1.32)</t>
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>41.09</v>
+        <v>53.57</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
@@ -4130,14 +4295,14 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>⚠️ Over 1.5 FT (prob 41% | conf 10% | odd 1.37)</t>
+          <t>🟡 Over 1.5 FT (prob 54% | conf 29% | odd 1.20)</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>41.37</v>
+        <v>51.57</v>
       </c>
       <c r="AN15" t="n">
-        <v>4.9</v>
+        <v>21.4</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -4146,14 +4311,14 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>⚠️ Over 2.5 FT (prob 41% | conf 5% | odd 2.16)</t>
+          <t>⚠️ Over 2.5 FT (prob 52% | conf 21% | odd 1.73)</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>57.19</v>
+        <v>49.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>37.3</v>
+        <v>25.7</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -4162,14 +4327,14 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>🟡 Under 1.5 HT (prob 57% | conf 37%)</t>
+          <t>🟡 Under 1.5 HT (prob 49% | conf 26%)</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>58.55</v>
+        <v>49</v>
       </c>
       <c r="AV15" t="n">
-        <v>36.1</v>
+        <v>21.4</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
@@ -4178,26 +4343,26 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>🟡 Under 2.5 FT (prob 59% | conf 36% | odd 1.64)</t>
+          <t>⚠️ Under 2.5 FT (prob 49% | conf 21% | odd 2.04)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Saint Martin</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>44.2</v>
+        <v>46.21</v>
       </c>
       <c r="D16" t="n">
-        <v>11.2</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4206,30 +4371,30 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 44% | conf 11% | odd 2.04)</t>
+          <t>⚠️ Ambas Marcam (prob 46% | conf 14% | odd 1.81)</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>44.02</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x0 (prob 44% | conf 13% | odd 7.28)</t>
+          <t>🔥 Lay 0x0 (prob 81% | conf 71% | odd 27.33)</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>50.96</v>
+        <v>47.4</v>
       </c>
       <c r="L16" t="n">
-        <v>9.1</v>
+        <v>2.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4238,30 +4403,30 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 51% | conf 9% | odd 9.50)</t>
+          <t>⚠️ Lay 0x1 (prob 47% | conf 2% | odd 10.67)</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>39.12</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>4.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>⚠️ Lay 1x0 (prob 39% | conf 5% | odd 5.67)</t>
+          <t>🔥 Lay 1x0 (prob 85% | conf 76% | odd 46.00)</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>95.53</v>
+        <v>96.55</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4270,14 +4435,14 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 15.33)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 19.67)</t>
         </is>
       </c>
       <c r="W16" t="n">
-        <v>76.98999999999999</v>
+        <v>16.63</v>
       </c>
       <c r="X16" t="n">
-        <v>70.90000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -4286,30 +4451,30 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 77% | conf 71%)</t>
+          <t>❌ Sem sinal — Lay Goleada Fora (4+) (prob 17%)</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>68.79000000000001</v>
+        <v>86.86</v>
       </c>
       <c r="AB16" t="n">
-        <v>63.2</v>
+        <v>84.5</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 69% | conf 63%)</t>
+          <t>🔥🔥 Lay Goleada Casa (4+) (prob 87% | conf 84%)</t>
         </is>
       </c>
       <c r="AE16" t="n">
-        <v>43.27</v>
+        <v>59.64</v>
       </c>
       <c r="AF16" t="n">
-        <v>7.3</v>
+        <v>34</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
@@ -4318,14 +4483,14 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 43% | conf 7% | odd 1.46)</t>
+          <t>🟡 Over 0.5 HT (prob 60% | conf 34% | odd 1.15)</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>39.96</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>8.199999999999999</v>
+        <v>51.2</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
@@ -4334,14 +4499,14 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>⚠️ Over 1.5 FT (prob 40% | conf 8% | odd 1.41)</t>
+          <t>🔥 Over 1.5 FT (prob 68% | conf 51% | odd 1.04)</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>38.82</v>
+        <v>69.48</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.7</v>
+        <v>50.5</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -4350,14 +4515,14 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>⚠️ Over 2.5 FT (prob 39% | conf 1% | odd 2.36)</t>
+          <t>🔥 Over 2.5 FT (prob 69% | conf 50% | odd 1.30)</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>57.44</v>
+        <v>37.82</v>
       </c>
       <c r="AR16" t="n">
-        <v>37.7</v>
+        <v>9</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -4366,14 +4531,14 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>🟡 Under 1.5 HT (prob 57% | conf 38%)</t>
+          <t>⚠️ Under 1.5 HT (prob 38% | conf 9%)</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>61.42</v>
+        <v>29.44</v>
       </c>
       <c r="AV16" t="n">
-        <v>40.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
@@ -4382,26 +4547,26 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>🟡 Under 2.5 FT (prob 61% | conf 40% | odd 1.58)</t>
+          <t>❌ Sem sinal — Under 2.5 FT (prob 29% | odd 3.27)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Independiente Medellín</t>
+          <t>Barra FC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jaguares de Córdoba</t>
+          <t>Nação</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45.71</v>
+        <v>46.53</v>
       </c>
       <c r="D17" t="n">
-        <v>13.6</v>
+        <v>14.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4410,14 +4575,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 46% | conf 14% | odd 1.98)</t>
+          <t>⚠️ Ambas Marcam (prob 47% | conf 15% | odd 1.97)</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>57.59</v>
+        <v>52.79</v>
       </c>
       <c r="H17" t="n">
-        <v>34.1</v>
+        <v>26.6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -4426,14 +4591,14 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 58% | conf 34% | odd 13.67)</t>
+          <t>🟡 Lay 0x0 (prob 53% | conf 27% | odd 8.50)</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>57.26</v>
+        <v>57.28</v>
       </c>
       <c r="L17" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4442,14 +4607,14 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 57% | conf 21% | odd 23.33)</t>
+          <t>⚠️ Lay 0x1 (prob 57% | conf 21% | odd 10.00)</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>46.19</v>
+        <v>40.34</v>
       </c>
       <c r="P17" t="n">
-        <v>15.8</v>
+        <v>6.7</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -4458,14 +4623,14 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>⚠️ Lay 1x0 (prob 46% | conf 16% | odd 6.83)</t>
+          <t>⚠️ Lay 1x0 (prob 40% | conf 7% | odd 4.30)</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>96.48999999999999</v>
+        <v>96.55</v>
       </c>
       <c r="T17" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -4474,30 +4639,30 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 17.67)</t>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 12.00)</t>
         </is>
       </c>
       <c r="W17" t="n">
-        <v>80.39</v>
+        <v>77.18000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>75.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 80% | conf 75%)</t>
+          <t>🔥 Lay Goleada Fora (4+) (prob 77% | conf 71%)</t>
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>31.51</v>
+        <v>48.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>19.3</v>
+        <v>39.2</v>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
@@ -4506,14 +4671,14 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>⚠️ Lay Goleada Casa (4+) (prob 32% | conf 19%)</t>
+          <t>🟡 Lay Goleada Casa (4+) (prob 48% | conf 39%)</t>
         </is>
       </c>
       <c r="AE17" t="n">
-        <v>56.46</v>
+        <v>49.37</v>
       </c>
       <c r="AF17" t="n">
-        <v>28.8</v>
+        <v>17.2</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
@@ -4522,14 +4687,14 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>🟡 Over 0.5 HT (prob 56% | conf 29% | odd 1.25)</t>
+          <t>⚠️ Over 0.5 HT (prob 49% | conf 17% | odd 1.32)</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>57.7</v>
+        <v>49.26</v>
       </c>
       <c r="AJ17" t="n">
-        <v>35.3</v>
+        <v>22.4</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
@@ -4538,14 +4703,14 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 58% | conf 35% | odd 1.18)</t>
+          <t>⚠️ Over 1.5 FT (prob 49% | conf 22% | odd 1.22)</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>56.9</v>
+        <v>48.98</v>
       </c>
       <c r="AN17" t="n">
-        <v>30.1</v>
+        <v>17.2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -4554,14 +4719,14 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 57% | conf 30% | odd 1.61)</t>
+          <t>⚠️ Over 2.5 FT (prob 49% | conf 17% | odd 1.82)</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>43.78</v>
+        <v>50.75</v>
       </c>
       <c r="AR17" t="n">
-        <v>17.7</v>
+        <v>27.9</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -4570,14 +4735,14 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 44% | conf 18%)</t>
+          <t>🟡 Under 1.5 HT (prob 51% | conf 28%)</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>43.94</v>
+        <v>51.35</v>
       </c>
       <c r="AV17" t="n">
-        <v>13.6</v>
+        <v>25</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
@@ -4586,26 +4751,26 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 44% | conf 14% | odd 2.27)</t>
+          <t>🟡 Under 2.5 FT (prob 51% | conf 25% | odd 1.92)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57.75</v>
+        <v>50.94</v>
       </c>
       <c r="D18" t="n">
-        <v>32.8</v>
+        <v>21.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4614,14 +4779,14 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟡 Ambas Marcam (prob 58% | conf 33% | odd 1.55)</t>
+          <t>⚠️ Ambas Marcam (prob 51% | conf 22% | odd 1.57)</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>57.31</v>
+        <v>57.77</v>
       </c>
       <c r="H18" t="n">
-        <v>33.7</v>
+        <v>34.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -4630,14 +4795,14 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>🟡 Lay 0x0 (prob 57% | conf 34% | odd 12.83)</t>
+          <t>🟡 Lay 0x0 (prob 58% | conf 34% | odd 12.00)</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>52.3</v>
+        <v>53.77</v>
       </c>
       <c r="L18" t="n">
-        <v>11.5</v>
+        <v>14.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4646,14 +4811,14 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 52% | conf 12% | odd 10.67)</t>
+          <t>⚠️ Lay 0x1 (prob 54% | conf 14% | odd 9.00)</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>60.41</v>
+        <v>63.56</v>
       </c>
       <c r="P18" t="n">
-        <v>38.1</v>
+        <v>43</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -4662,30 +4827,30 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>🟡 Lay 1x0 (prob 60% | conf 38% | odd 9.00)</t>
+          <t>🟡 Lay 1x0 (prob 64% | conf 43% | odd 9.00)</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>94.40000000000001</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐⭐⭐</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>⚠️ Lay 2x2 (prob 94% | conf 1% | odd 10.67)</t>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 10.00)</t>
         </is>
       </c>
       <c r="W18" t="n">
-        <v>56.25</v>
+        <v>47.88</v>
       </c>
       <c r="X18" t="n">
-        <v>44.6</v>
+        <v>34</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -4694,14 +4859,14 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Fora (4+) (prob 56% | conf 45%)</t>
+          <t>🟡 Lay Goleada Fora (4+) (prob 48% | conf 34%)</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>55.58</v>
+        <v>59.76</v>
       </c>
       <c r="AB18" t="n">
-        <v>47.6</v>
+        <v>52.6</v>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
@@ -4710,14 +4875,14 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>🟡 Lay Goleada Casa (4+) (prob 56% | conf 48%)</t>
+          <t>🔥 Lay Goleada Casa (4+) (prob 60% | conf 53%)</t>
         </is>
       </c>
       <c r="AE18" t="n">
-        <v>52.91</v>
+        <v>54.74</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
@@ -4726,14 +4891,14 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>⚠️ Over 0.5 HT (prob 53% | conf 23% | odd 1.27)</t>
+          <t>🟡 Over 0.5 HT (prob 55% | conf 26% | odd 1.30)</t>
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>54.74</v>
+        <v>53.87</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30.8</v>
+        <v>29.5</v>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
@@ -4742,14 +4907,14 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>🟡 Over 1.5 FT (prob 55% | conf 31% | odd 1.16)</t>
+          <t>🟡 Over 1.5 FT (prob 54% | conf 30% | odd 1.19)</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>54.34</v>
+        <v>55.47</v>
       </c>
       <c r="AN18" t="n">
-        <v>25.9</v>
+        <v>27.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -4758,14 +4923,14 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>🟡 Over 2.5 FT (prob 54% | conf 26% | odd 1.62)</t>
+          <t>🟡 Over 2.5 FT (prob 55% | conf 28% | odd 1.67)</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>46.8</v>
+        <v>46.46</v>
       </c>
       <c r="AR18" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -4774,14 +4939,14 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>⚠️ Under 1.5 HT (prob 47% | conf 22%)</t>
+          <t>⚠️ Under 1.5 HT (prob 46% | conf 22%)</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>46.8</v>
+        <v>42.99</v>
       </c>
       <c r="AV18" t="n">
-        <v>18</v>
+        <v>12.1</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
@@ -4790,26 +4955,26 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>⚠️ Under 2.5 FT (prob 47% | conf 18% | odd 2.18)</t>
+          <t>⚠️ Under 2.5 FT (prob 43% | conf 12% | odd 2.09)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>44.65</v>
+        <v>50.69</v>
       </c>
       <c r="D19" t="n">
-        <v>11.9</v>
+        <v>21.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4818,14 +4983,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>⚠️ Ambas Marcam (prob 45% | conf 12% | odd 2.04)</t>
+          <t>⚠️ Ambas Marcam (prob 51% | conf 22% | odd 1.87)</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>38.6</v>
+        <v>61.18</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>39.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -4834,14 +4999,14 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x0 (prob 39% | conf 5% | odd 7.20)</t>
+          <t>🟡 Lay 0x0 (prob 61% | conf 40% | odd 12.00)</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>48.79</v>
+        <v>54.34</v>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>15.3</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4850,14 +5015,14 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>⚠️ Lay 0x1 (prob 49% | conf 5% | odd 8.17)</t>
+          <t>⚠️ Lay 0x1 (prob 54% | conf 15% | odd 11.33)</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>39.5</v>
+        <v>56.4</v>
       </c>
       <c r="P19" t="n">
-        <v>5.4</v>
+        <v>31.8</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -4866,135 +5031,1155 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>⚠️ Lay 1x0 (prob 40% | conf 5% | odd 6.00)</t>
+          <t>🟡 Lay 1x0 (prob 56% | conf 32% | odd 9.00)</t>
         </is>
       </c>
       <c r="S19" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 13.67)</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>61.53</v>
+      </c>
+      <c r="X19" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 62% | conf 51%)</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>🟡 Lay Goleada Casa (4+) (prob 48% | conf 39%)</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>53.47</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>⚠️ Over 0.5 HT (prob 53% | conf 24% | odd 1.28)</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
+        <v>54.61</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>🟡 Over 1.5 FT (prob 55% | conf 31% | odd 1.19)</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>⚠️ Over 2.5 FT (prob 53% | conf 23% | odd 1.69)</t>
+        </is>
+      </c>
+      <c r="AQ19" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>⚠️ Under 1.5 HT (prob 48% | conf 24%)</t>
+        </is>
+      </c>
+      <c r="AU19" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>⚠️ Under 2.5 FT (prob 47% | conf 18% | odd 2.13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Rionegro Águilas</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>⚠️ Ambas Marcam (prob 48% | conf 17% | odd 1.91)</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="H20" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>🟡 Lay 0x0 (prob 63% | conf 42% | odd 9.83)</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 0x1 (prob 56% | conf 18% | odd 12.67)</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 1x0 (prob 46% | conf 16% | odd 6.00)</t>
+        </is>
+      </c>
+      <c r="S20" t="n">
+        <v>96.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 2x2 (prob 97% | conf 2% | odd 14.67)</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>82.01000000000001</v>
+      </c>
+      <c r="X20" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 82% | conf 77%)</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>🟡 Lay Goleada Casa (4+) (prob 45% | conf 35%)</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>⚠️ Over 0.5 HT (prob 51% | conf 20% | odd 1.35)</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>🟡 Over 1.5 FT (prob 52% | conf 26% | odd 1.28)</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>⚠️ Over 2.5 FT (prob 47% | conf 14% | odd 1.95)</t>
+        </is>
+      </c>
+      <c r="AQ20" t="n">
+        <v>53.31</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>🟡 Under 1.5 HT (prob 53% | conf 32%)</t>
+        </is>
+      </c>
+      <c r="AU20" t="n">
+        <v>52.79</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>🟡 Under 2.5 FT (prob 53% | conf 27% | odd 1.84)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Firpo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cacahuatique</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="D21" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>⚠️ Ambas Marcam (prob 48% | conf 18% | odd 1.87)</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>52.32</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>🟡 Lay 0x0 (prob 52% | conf 26% | odd 10.17)</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 0x1 (prob 53% | conf 13% | odd 12.33)</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="P21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 1x0 (prob 47% | conf 18% | odd 6.17)</t>
+        </is>
+      </c>
+      <c r="S21" t="n">
         <v>95.53</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="U19" t="inlineStr">
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>⭐⭐⭐⭐</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 14.67)</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>75.42</v>
-      </c>
-      <c r="X19" t="n">
-        <v>68.90000000000001</v>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>🔥 Lay Goleada Fora (4+) (prob 75% | conf 69%)</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>77.88</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>🔥 Lay Goleada Casa (4+) (prob 78% | conf 74%)</t>
-        </is>
-      </c>
-      <c r="AE19" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>⚠️ Over 0.5 HT (prob 42% | conf 6% | odd 1.46)</t>
-        </is>
-      </c>
-      <c r="AI19" t="n">
-        <v>39.05</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>⚠️ Over 1.5 FT (prob 39% | conf 7% | odd 1.43)</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>36.32</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>❌ Sem sinal — Over 2.5 FT (prob 36% | odd 2.43)</t>
-        </is>
-      </c>
-      <c r="AQ19" t="n">
-        <v>59.19</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>🟡 Under 1.5 HT (prob 59% | conf 40%)</t>
-        </is>
-      </c>
-      <c r="AU19" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>⭐</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>🟡 Under 2.5 FT (prob 63% | conf 43% | odd 1.53)</t>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 13.67)</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="X21" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 69% | conf 61%)</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>🟡 Lay Goleada Casa (4+) (prob 48% | conf 38%)</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>⚠️ Over 0.5 HT (prob 51% | conf 20% | odd 1.34)</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>🟡 Over 1.5 FT (prob 52% | conf 27% | odd 1.24)</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>⚠️ Over 2.5 FT (prob 51% | conf 20% | odd 1.80)</t>
+        </is>
+      </c>
+      <c r="AQ21" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>🟡 Under 1.5 HT (prob 50% | conf 27%)</t>
+        </is>
+      </c>
+      <c r="AU21" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>⚠️ Under 2.5 FT (prob 49% | conf 22% | odd 1.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Alianza</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fuerte San Francisco</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>⚠️ Ambas Marcam (prob 46% | conf 15% | odd 1.97)</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="H22" t="n">
+        <v>23</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 0x0 (prob 50% | conf 23% | odd 9.50)</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="L22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 0x1 (prob 51% | conf 9% | odd 11.67)</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 1x0 (prob 40% | conf 6% | odd 5.33)</t>
+        </is>
+      </c>
+      <c r="S22" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 15.00)</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 78% | conf 72%)</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>53.07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>🟡 Lay Goleada Casa (4+) (prob 53% | conf 45%)</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>47.95</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>⚠️ Over 0.5 HT (prob 48% | conf 15% | odd 1.36)</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>⚠️ Over 1.5 FT (prob 46% | conf 18% | odd 1.29)</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>⚠️ Over 2.5 FT (prob 44% | conf 10% | odd 1.93)</t>
+        </is>
+      </c>
+      <c r="AQ22" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>🟡 Under 1.5 HT (prob 54% | conf 33%)</t>
+        </is>
+      </c>
+      <c r="AU22" t="n">
+        <v>56.88</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>🟡 Under 2.5 FT (prob 57% | conf 34% | odd 1.80)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>59.14</v>
+      </c>
+      <c r="D23" t="n">
+        <v>35</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>🟡 Ambas Marcam (prob 59% | conf 35% | odd 1.51)</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="H23" t="n">
+        <v>39</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>🟡 Lay 0x0 (prob 61% | conf 39% | odd 14.00)</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="L23" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 0x1 (prob 54% | conf 14% | odd 13.17)</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="P23" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>🟡 Lay 1x0 (prob 55% | conf 30% | odd 9.17)</t>
+        </is>
+      </c>
+      <c r="S23" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 2x2 (prob 93% | conf 0% | odd 10.33)</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="X23" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 64% | conf 55%)</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>45.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>🟡 Lay Goleada Casa (4+) (prob 45% | conf 35%)</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>57.18</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>🟡 Over 0.5 HT (prob 57% | conf 30% | odd 1.24)</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>🟡 Over 1.5 FT (prob 62% | conf 41% | odd 1.17)</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>🟡 Over 2.5 FT (prob 58% | conf 31% | odd 1.53)</t>
+        </is>
+      </c>
+      <c r="AQ23" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>⚠️ Under 1.5 HT (prob 44% | conf 18%)</t>
+        </is>
+      </c>
+      <c r="AU23" t="n">
+        <v>41.15</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>⚠️ Under 2.5 FT (prob 41% | conf 9% | odd 2.45)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Vancouver FC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>56.94</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>🟡 Ambas Marcam (prob 57% | conf 32% | odd 1.51)</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="H24" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>🟡 Lay 0x0 (prob 60% | conf 38% | odd 14.83)</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="L24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 0x1 (prob 55% | conf 16% | odd 12.33)</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>🟡 Lay 1x0 (prob 57% | conf 33% | odd 8.83)</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>95.53</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>⚠️ Lay 2x2 (prob 96% | conf 1% | odd 10.33)</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="X24" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>🔥 Lay Goleada Fora (4+) (prob 62% | conf 52%)</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>44.37</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>🟡 Lay Goleada Casa (4+) (prob 44% | conf 34%)</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>56.93</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>🟡 Over 0.5 HT (prob 57% | conf 30% | odd 1.24)</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>58.59</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>🟡 Over 1.5 FT (prob 59% | conf 37% | odd 1.13)</t>
+        </is>
+      </c>
+      <c r="AM24" t="n">
+        <v>59.06</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>🟡 Over 2.5 FT (prob 59% | conf 34% | odd 1.52)</t>
+        </is>
+      </c>
+      <c r="AQ24" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>⚠️ Under 1.5 HT (prob 46% | conf 20%)</t>
+        </is>
+      </c>
+      <c r="AU24" t="n">
+        <v>41.26</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>⭐</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>⚠️ Under 2.5 FT (prob 41% | conf 10% | odd 2.34)</t>
         </is>
       </c>
     </row>
